--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.43749942998336</v>
+        <v>4.296093657372296</v>
       </c>
       <c r="D2" t="n">
-        <v>12.55331787797018</v>
+        <v>2.039914155170154</v>
       </c>
       <c r="E2" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F2" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.7284095875509</v>
+        <v>2.718366557977022</v>
       </c>
       <c r="D3" t="n">
-        <v>14.23024947075771</v>
+        <v>2.312415538998128</v>
       </c>
       <c r="E3" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F3" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.922588181914916</v>
+        <v>1.612420579561174</v>
       </c>
       <c r="D4" t="n">
-        <v>2.142529968920763</v>
+        <v>0.3481611199496241</v>
       </c>
       <c r="E4" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F4" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.40669621773552</v>
+        <v>5.428588135382022</v>
       </c>
       <c r="D5" t="n">
-        <v>21.48656442342831</v>
+        <v>3.491566718807101</v>
       </c>
       <c r="E5" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F5" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.91220186542579</v>
+        <v>3.39823280313169</v>
       </c>
       <c r="D6" t="n">
-        <v>20.56989483036347</v>
+        <v>3.342607909934065</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F6" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.97620475055592</v>
+        <v>4.871133271965336</v>
       </c>
       <c r="D7" t="n">
-        <v>6.158443599930552</v>
+        <v>1.000747084988715</v>
       </c>
       <c r="E7" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F7" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.84460231924449</v>
+        <v>6.149747876877231</v>
       </c>
       <c r="D8" t="n">
-        <v>21.76284840375265</v>
+        <v>3.536462865609805</v>
       </c>
       <c r="E8" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F8" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.17144815652687</v>
+        <v>4.090360325435618</v>
       </c>
       <c r="D9" t="n">
-        <v>19.35400398376955</v>
+        <v>3.145025647362552</v>
       </c>
       <c r="E9" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F9" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.93630210290385</v>
+        <v>10.87714909172188</v>
       </c>
       <c r="D10" t="n">
-        <v>22.44953786542008</v>
+        <v>3.648049903130764</v>
       </c>
       <c r="E10" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F10" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.25582288217169</v>
+        <v>7.029071218352899</v>
       </c>
       <c r="D11" t="n">
-        <v>30.16594883528149</v>
+        <v>4.901966685733242</v>
       </c>
       <c r="E11" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F11" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.57860283262511</v>
+        <v>9.194022960301581</v>
       </c>
       <c r="D12" t="n">
-        <v>21.2741792543883</v>
+        <v>3.4570541288381</v>
       </c>
       <c r="E12" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F12" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.69473458241242</v>
+        <v>8.075394369642018</v>
       </c>
       <c r="D13" t="n">
-        <v>20.09549198666062</v>
+        <v>3.26551744783235</v>
       </c>
       <c r="E13" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F13" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.8425239783049</v>
+        <v>7.124410146474546</v>
       </c>
       <c r="D14" t="n">
-        <v>14.20329398733628</v>
+        <v>2.308035272942146</v>
       </c>
       <c r="E14" t="n">
-        <v>15.71946619651923</v>
+        <v>2.554413256934375</v>
       </c>
       <c r="F14" t="n">
-        <v>7.142817451162633</v>
+        <v>1.160707835813928</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
